--- a/测试用例清单.xlsx
+++ b/测试用例清单.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Practice\my-compiler\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\root\my-compiler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8BB8338-F376-49FF-9E75-504FB31CB351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2EFE4C-80F4-4BFC-8CD1-81106013DAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" r:id="rId1"/>
@@ -29,19 +29,14 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="289">
   <si>
     <r>
       <t xml:space="preserve">Test  Case Form </t>
@@ -2569,6 +2564,66 @@
   <si>
     <t>黑盒；场景法：数组声明→数组实参→函数调用→多级寻址→IR/优化。</t>
   </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>POK</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺少0</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>return 15</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>缺少</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="3"/>
+      </rPr>
+      <t>sdiv</t>
+    </r>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>识别成功</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>顺序正确</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>无误</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确跳转</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>可承受压力</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2578,7 +2633,7 @@
     <numFmt numFmtId="176" formatCode="yy\.mm\.dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\.mm\.dd"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <name val="Arial"/>
@@ -2700,6 +2755,29 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
@@ -2943,7 +3021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -3072,16 +3150,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3101,6 +3173,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3299,13 +3383,13 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-2.7466658528397473E-5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>-2.0345672983998128E-6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>-1.0172836491999064E-6</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -4237,12 +4321,12 @@
       <c r="K34" s="26"/>
     </row>
     <row r="37" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="58"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="56"/>
     </row>
     <row r="38" spans="2:11" ht="16" x14ac:dyDescent="0.35">
       <c r="B38" s="27" t="s">
@@ -4250,14 +4334,14 @@
       </c>
       <c r="C38" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=OK"))</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D38" s="27" t="s">
         <v>40</v>
       </c>
       <c r="E38" s="29">
         <f>IF(E13=0,0,C38/E13)</f>
-        <v>0</v>
+        <v>-2.7466658528397473E-5</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="16" x14ac:dyDescent="0.35">
@@ -4266,14 +4350,14 @@
       </c>
       <c r="C39" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=POK"))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39" s="27" t="s">
         <v>42</v>
       </c>
       <c r="E39" s="29">
         <f>IF(E13=0,0,C39/E13)</f>
-        <v>0</v>
+        <v>-2.0345672983998128E-6</v>
       </c>
     </row>
     <row r="40" spans="2:11" ht="16" x14ac:dyDescent="0.35">
@@ -4282,14 +4366,14 @@
       </c>
       <c r="C40" s="28">
         <f>IF($E$13=0,0,COUNTIF('Test Cases测试用例'!$L:$L,"=NG"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40" s="27" t="s">
         <v>44</v>
       </c>
       <c r="E40" s="29">
         <f>IF(E13=0,0,C40/E13)</f>
-        <v>0</v>
+        <v>-1.0172836491999064E-6</v>
       </c>
     </row>
     <row r="41" spans="2:11" ht="16" x14ac:dyDescent="0.35">
@@ -4318,12 +4402,12 @@
       <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="59">
+      <c r="C43" s="57">
         <f>E13</f>
         <v>-983010</v>
       </c>
-      <c r="D43" s="60"/>
-      <c r="E43" s="61"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4527,39 +4611,43 @@
       <c r="EJ1" s="38"/>
     </row>
     <row r="2" spans="1:140" ht="77" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="52">
+      <c r="A2" s="39">
         <v>1</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="C2" s="53" t="s">
+      <c r="C2" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="D2" s="53" t="s">
+      <c r="D2" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G2" s="53" t="s">
+      <c r="G2" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="53" t="s">
+      <c r="H2" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="J2" s="53" t="s">
+      <c r="J2" s="47" t="s">
         <v>182</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="M2" s="53" t="s">
+      <c r="K2" s="63" t="s">
+        <v>284</v>
+      </c>
+      <c r="L2" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M2" s="47" t="s">
         <v>183</v>
       </c>
       <c r="N2" s="5" t="s">
@@ -4567,39 +4655,43 @@
       </c>
     </row>
     <row r="3" spans="1:140" ht="76.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="52">
+      <c r="A3" s="39">
         <v>2</v>
       </c>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="53" t="s">
+      <c r="C3" s="47" t="s">
         <v>184</v>
       </c>
-      <c r="D3" s="53" t="s">
+      <c r="D3" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="H3" s="53" t="s">
+      <c r="H3" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="I3" s="53" t="s">
+      <c r="I3" s="47" t="s">
         <v>188</v>
       </c>
-      <c r="J3" s="53" t="s">
+      <c r="J3" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-      <c r="M3" s="53" t="s">
+      <c r="K3" s="63" t="s">
+        <v>285</v>
+      </c>
+      <c r="L3" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M3" s="47" t="s">
         <v>190</v>
       </c>
       <c r="N3" s="5" t="s">
@@ -4607,39 +4699,43 @@
       </c>
     </row>
     <row r="4" spans="1:140" ht="87" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="52">
+      <c r="A4" s="39">
         <v>3</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="47" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="47" t="s">
         <v>194</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="47" t="s">
         <v>195</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="47" t="s">
         <v>196</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L4" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M4" s="47" t="s">
         <v>197</v>
       </c>
       <c r="N4" s="5" t="s">
@@ -4647,39 +4743,43 @@
       </c>
     </row>
     <row r="5" spans="1:140" ht="81" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="52">
+      <c r="A5" s="39">
         <v>4</v>
       </c>
-      <c r="B5" s="53" t="s">
+      <c r="B5" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="H5" s="53" t="s">
+      <c r="H5" s="47" t="s">
         <v>201</v>
       </c>
-      <c r="I5" s="53" t="s">
+      <c r="I5" s="47" t="s">
         <v>202</v>
       </c>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53" t="s">
+      <c r="K5" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M5" s="47" t="s">
         <v>204</v>
       </c>
       <c r="N5" s="5" t="s">
@@ -4687,409 +4787,453 @@
       </c>
     </row>
     <row r="6" spans="1:140" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="52">
+      <c r="A6" s="39">
         <v>5</v>
       </c>
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="47" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="D6" s="53" t="s">
+      <c r="D6" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="53" t="s">
+      <c r="E6" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G6" s="53" t="s">
+      <c r="G6" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" s="47" t="s">
         <v>209</v>
       </c>
-      <c r="J6" s="53" t="s">
+      <c r="J6" s="47" t="s">
         <v>210</v>
       </c>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-      <c r="M6" s="53" t="s">
+      <c r="K6" s="61" t="s">
+        <v>280</v>
+      </c>
+      <c r="L6" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="M6" s="47" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="52">
+      <c r="A7" s="39">
         <v>6</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="53" t="s">
+      <c r="D7" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="53" t="s">
+      <c r="E7" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="I7" s="53" t="s">
+      <c r="I7" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="J7" s="53" t="s">
+      <c r="J7" s="47" t="s">
         <v>217</v>
       </c>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53" t="s">
+      <c r="K7" s="60" t="s">
+        <v>281</v>
+      </c>
+      <c r="L7" s="60" t="s">
+        <v>282</v>
+      </c>
+      <c r="M7" s="47" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="52">
+      <c r="A8" s="39">
         <v>7</v>
       </c>
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="53" t="s">
+      <c r="C8" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="53" t="s">
+      <c r="D8" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="53" t="s">
+      <c r="E8" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="I8" s="53" t="s">
+      <c r="I8" s="47" t="s">
         <v>223</v>
       </c>
-      <c r="J8" s="53" t="s">
+      <c r="J8" s="47" t="s">
         <v>224</v>
       </c>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53" t="s">
+      <c r="K8" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M8" s="47" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="52">
+      <c r="A9" s="39">
         <v>8</v>
       </c>
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="53" t="s">
+      <c r="C9" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="53" t="s">
+      <c r="E9" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="53" t="s">
+      <c r="G9" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="H9" s="53" t="s">
+      <c r="H9" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="I9" s="53" t="s">
+      <c r="I9" s="47" t="s">
         <v>230</v>
       </c>
-      <c r="J9" s="53" t="s">
+      <c r="J9" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-      <c r="M9" s="53" t="s">
+      <c r="K9" s="63" t="s">
+        <v>287</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M9" s="47" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="55">
+      <c r="A10" s="53">
         <v>9</v>
       </c>
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="53" t="s">
+      <c r="D10" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="H10" s="53" t="s">
+      <c r="H10" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="I10" s="53" t="s">
+      <c r="I10" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="J10" s="53" t="s">
+      <c r="J10" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-      <c r="M10" s="53" t="s">
+      <c r="K10" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L10" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M10" s="47" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="52">
+      <c r="A11" s="39">
         <v>10</v>
       </c>
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="47" t="s">
         <v>191</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="47" t="s">
         <v>185</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G11" s="53" t="s">
+      <c r="G11" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="H11" s="53" t="s">
+      <c r="H11" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="I11" s="53" t="s">
+      <c r="I11" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="J11" s="53" t="s">
+      <c r="J11" s="47" t="s">
         <v>242</v>
       </c>
-      <c r="K11" s="53"/>
-      <c r="L11" s="53"/>
-      <c r="M11" s="53" t="s">
+      <c r="K11" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L11" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M11" s="47" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="12" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="52">
+      <c r="A12" s="39">
         <v>11</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="47" t="s">
         <v>245</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G12" s="53" t="s">
+      <c r="G12" s="47" t="s">
         <v>246</v>
       </c>
-      <c r="H12" s="53" t="s">
+      <c r="H12" s="47" t="s">
         <v>247</v>
       </c>
-      <c r="I12" s="53" t="s">
+      <c r="I12" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="J12" s="53" t="s">
+      <c r="J12" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53" t="s">
+      <c r="K12" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L12" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M12" s="47" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="52">
+      <c r="A13" s="39">
         <v>12</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="47" t="s">
         <v>244</v>
       </c>
-      <c r="C13" s="53" t="s">
+      <c r="C13" s="47" t="s">
         <v>251</v>
       </c>
-      <c r="D13" s="53" t="s">
+      <c r="D13" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="53" t="s">
+      <c r="E13" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="H13" s="53" t="s">
+      <c r="H13" s="47" t="s">
         <v>253</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="47" t="s">
         <v>254</v>
       </c>
-      <c r="J13" s="53" t="s">
+      <c r="J13" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53" t="s">
+      <c r="K13" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L13" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M13" s="47" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="52">
+      <c r="A14" s="39">
         <v>13</v>
       </c>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="47" t="s">
         <v>257</v>
       </c>
-      <c r="C14" s="53" t="s">
+      <c r="C14" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="D14" s="53" t="s">
+      <c r="D14" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="53" t="s">
+      <c r="E14" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G14" s="53" t="s">
+      <c r="G14" s="47" t="s">
         <v>259</v>
       </c>
-      <c r="H14" s="53" t="s">
+      <c r="H14" s="47" t="s">
         <v>260</v>
       </c>
-      <c r="I14" s="53" t="s">
+      <c r="I14" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="J14" s="53" t="s">
+      <c r="J14" s="47" t="s">
         <v>262</v>
       </c>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53" t="s">
+      <c r="K14" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L14" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M14" s="47" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="52">
+      <c r="A15" s="39">
         <v>14</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="53" t="s">
+      <c r="E15" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G15" s="53" t="s">
+      <c r="G15" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="H15" s="53" t="s">
+      <c r="H15" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="I15" s="53" t="s">
+      <c r="I15" s="47" t="s">
         <v>268</v>
       </c>
-      <c r="J15" s="53" t="s">
+      <c r="J15" s="47" t="s">
         <v>269</v>
       </c>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53" t="s">
+      <c r="K15" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L15" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M15" s="47" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:140" ht="96" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="52">
+      <c r="A16" s="39">
         <v>15</v>
       </c>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C16" s="53" t="s">
+      <c r="C16" s="47" t="s">
         <v>272</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="53" t="s">
+      <c r="E16" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="G16" s="53" t="s">
+      <c r="G16" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="H16" s="53" t="s">
+      <c r="H16" s="47" t="s">
         <v>274</v>
       </c>
-      <c r="I16" s="53" t="s">
+      <c r="I16" s="47" t="s">
         <v>275</v>
       </c>
-      <c r="J16" s="53" t="s">
+      <c r="J16" s="47" t="s">
         <v>276</v>
       </c>
-      <c r="K16" s="53"/>
-      <c r="L16" s="53"/>
-      <c r="M16" s="53" t="s">
+      <c r="K16" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L16" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="M16" s="47" t="s">
         <v>277</v>
       </c>
     </row>
@@ -5120,8 +5264,12 @@
       <c r="J17" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
+      <c r="K17" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L17" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M17" s="48" t="s">
         <v>72</v>
       </c>
@@ -5153,8 +5301,12 @@
       <c r="J18" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="K18" s="47"/>
-      <c r="L18" s="47"/>
+      <c r="K18" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L18" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M18" s="47" t="s">
         <v>78</v>
       </c>
@@ -5186,8 +5338,12 @@
       <c r="J19" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
+      <c r="K19" s="62" t="s">
+        <v>283</v>
+      </c>
+      <c r="L19" s="60" t="s">
+        <v>279</v>
+      </c>
       <c r="M19" s="48" t="s">
         <v>85</v>
       </c>
@@ -5219,8 +5375,12 @@
       <c r="J20" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
+      <c r="K20" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L20" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M20" s="47" t="s">
         <v>91</v>
       </c>
@@ -5252,8 +5412,12 @@
       <c r="J21" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="K21" s="47"/>
-      <c r="L21" s="47"/>
+      <c r="K21" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L21" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M21" s="48" t="s">
         <v>97</v>
       </c>
@@ -5285,8 +5449,12 @@
       <c r="J22" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="K22" s="47"/>
-      <c r="L22" s="47"/>
+      <c r="K22" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L22" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M22" s="48" t="s">
         <v>103</v>
       </c>
@@ -5318,8 +5486,12 @@
       <c r="J23" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L23" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M23" s="47" t="s">
         <v>110</v>
       </c>
@@ -5351,8 +5523,12 @@
       <c r="J24" s="51" t="s">
         <v>116</v>
       </c>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
+      <c r="K24" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L24" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M24" s="47" t="s">
         <v>117</v>
       </c>
@@ -5384,8 +5560,12 @@
       <c r="J25" s="51" t="s">
         <v>123</v>
       </c>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
+      <c r="K25" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L25" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M25" s="47" t="s">
         <v>124</v>
       </c>
@@ -5417,8 +5597,12 @@
       <c r="J26" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
+      <c r="K26" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L26" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M26" s="47" t="s">
         <v>131</v>
       </c>
@@ -5450,8 +5634,12 @@
       <c r="J27" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
+      <c r="K27" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L27" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M27" s="47" t="s">
         <v>138</v>
       </c>
@@ -5483,8 +5671,12 @@
       <c r="J28" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
+      <c r="K28" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L28" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M28" s="47" t="s">
         <v>144</v>
       </c>
@@ -5516,8 +5708,12 @@
       <c r="J29" s="51" t="s">
         <v>150</v>
       </c>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
+      <c r="K29" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L29" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M29" s="47" t="s">
         <v>151</v>
       </c>
@@ -5549,8 +5745,12 @@
       <c r="J30" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
+      <c r="K30" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="L30" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M30" s="47" t="s">
         <v>157</v>
       </c>
@@ -5582,8 +5782,12 @@
       <c r="J31" s="47" t="s">
         <v>163</v>
       </c>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
+      <c r="K31" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="L31" s="60" t="s">
+        <v>278</v>
+      </c>
       <c r="M31" s="47" t="s">
         <v>164</v>
       </c>
